--- a/05_Visualizations/Bibliometric_Analysis_Master_Data.xlsx
+++ b/05_Visualizations/Bibliometric_Analysis_Master_Data.xlsx
@@ -5,27 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rao\Documents\Towards PHD Cyber Security and CNI\Proposals\Journal Submition paper\SLR 2026\Qasim ALL Files for SLR Submission\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rao\Documents\Towards PHD Cyber Security and CNI\Proposals\Journal Submition paper\SLR 2026\PLOS One\SLR-Insider-Threat-Detection-ML-Supplement Alriyami Murtadha - Final Copy\05_Visualizations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C83678-30DC-49D7-B92D-5D023813A6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BF410CC-7FE6-4981-8D5F-43D9A3A3F35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{A31D2125-A59A-4719-8AF0-8461B77889D6}"/>
+    <workbookView xWindow="-28920" yWindow="-75" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{A31D2125-A59A-4719-8AF0-8461B77889D6}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
-    <sheet name="Journal Source of Papers" sheetId="3" r:id="rId2"/>
-    <sheet name="Publisher Source " sheetId="4" r:id="rId3"/>
-    <sheet name="Qartile Distribution" sheetId="5" r:id="rId4"/>
-    <sheet name="Journal Namd and Paper Count" sheetId="6" r:id="rId5"/>
-    <sheet name="KeyWords Analysis" sheetId="7" r:id="rId6"/>
-    <sheet name="Publication Year Analysis" sheetId="8" r:id="rId7"/>
+    <sheet name="Journal Source of Papers" sheetId="3" r:id="rId1"/>
+    <sheet name="Publisher Source " sheetId="4" r:id="rId2"/>
+    <sheet name="Qartile Distribution" sheetId="5" r:id="rId3"/>
+    <sheet name="Journal Namd and Paper Count" sheetId="6" r:id="rId4"/>
+    <sheet name="Publication Year Analysis" sheetId="8" r:id="rId5"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">'KeyWords Analysis'!$B$2:$B$11</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'KeyWords Analysis'!$E$1</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'KeyWords Analysis'!$E$2:$E$11</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -47,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="281">
   <si>
     <t>ISSN</t>
   </si>
@@ -106,189 +99,57 @@
     <t>1556-6013</t>
   </si>
   <si>
-    <t>Author(s) (Year)</t>
-  </si>
-  <si>
-    <t>Document Title</t>
-  </si>
-  <si>
-    <t>Journal/Source</t>
-  </si>
-  <si>
-    <t>Quartile</t>
-  </si>
-  <si>
-    <t>Sarhan &amp; Altwaijry (2023)</t>
-  </si>
-  <si>
     <t>Insider Threat Detection Using Machine Learning Approach</t>
   </si>
   <si>
-    <t>Applied Sciences-Basel</t>
-  </si>
-  <si>
-    <t>Q2</t>
-  </si>
-  <si>
-    <t>Kong et al. (2025)</t>
-  </si>
-  <si>
     <t>DPI-ITD: A Dual-Perspective Information-Driven Framework for Insider Threat Detection in IoT Systems</t>
   </si>
   <si>
-    <t>IEEE Internet of Things Journal</t>
-  </si>
-  <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>He et al. (2024)</t>
-  </si>
-  <si>
     <t>Double-Layer Detection of Internal Threat in Enterprise Systems Based on Deep Learning</t>
   </si>
   <si>
-    <t>IEEE Trans. Info. Forensics &amp; Security</t>
-  </si>
-  <si>
-    <t>Ye et al. (2025)</t>
-  </si>
-  <si>
     <t>Research on insider threat detection based on personalized federated learning and behavior log analysis</t>
   </si>
   <si>
     <t>Scientific Reports</t>
   </si>
   <si>
-    <t>Ferraro et al. (2025)</t>
-  </si>
-  <si>
     <t>Generative Agent-Based Modeling with Large Language Models for insider threat detection</t>
   </si>
   <si>
-    <t>Engineering Apps. of AI</t>
-  </si>
-  <si>
-    <t>Al Hammadi et al. (2021)</t>
-  </si>
-  <si>
     <t>Explainable artificial intelligence to evaluate industrial internal security using EEG signals in IoT framework</t>
   </si>
   <si>
-    <t>Ad Hoc Networks</t>
-  </si>
-  <si>
-    <t>Gayathri et al. (2024)</t>
-  </si>
-  <si>
     <t>Hybrid deep learning model using SPCAGAN augmentation for insider threat analysis</t>
   </si>
   <si>
-    <t>Expert Systems with Applications</t>
-  </si>
-  <si>
-    <t>Wang &amp; El Saddik (2023)</t>
-  </si>
-  <si>
     <t>DTITD: An Intelligent Insider Threat Detection Framework Based on Digital Twin and Self-Attention Based Deep Learning Models</t>
   </si>
   <si>
-    <t>IEEE Access</t>
-  </si>
-  <si>
-    <t>Nasir et al. (2021)</t>
-  </si>
-  <si>
     <t>Behavioral Based Insider Threat Detection Using Deep Learning</t>
   </si>
   <si>
-    <t>Song et al. (2024)</t>
-  </si>
-  <si>
     <t>BRITD: behavior rhythm insider threat detection with time awareness and user adaptation</t>
   </si>
   <si>
     <t>Cybersecurity</t>
   </si>
   <si>
-    <t>Wei et al. (2024)</t>
-  </si>
-  <si>
     <t>E-Watcher: insider threat monitoring and detection for enhanced security</t>
   </si>
   <si>
-    <t>Annals of Telecommunications</t>
-  </si>
-  <si>
-    <t>Anju &amp; Krishnamurthy (2024)</t>
-  </si>
-  <si>
     <t>M-EOS: modified-equilibrium optimization-based stacked CNN for insider threat detection</t>
   </si>
   <si>
-    <t>Wireless Networks</t>
-  </si>
-  <si>
-    <t>Pal et al. (2023)</t>
-  </si>
-  <si>
     <t>Temporal feature aggregation with attention for insider threat detection from activity logs</t>
   </si>
   <si>
-    <t>Wang et al. (2023)</t>
-  </si>
-  <si>
     <t>Insider Threat Detection Based on Deep Clustering of Multi-Source Behavioral Events</t>
   </si>
   <si>
-    <t>Al-Mhiqani et al. (2021)</t>
-  </si>
-  <si>
     <t>An Integrated Imbalanced Learning and Deep Neural Network Model for Insider Threat Detection</t>
   </si>
   <si>
-    <t>Int. J. Adv. Comp. Science &amp; Apps</t>
-  </si>
-  <si>
-    <t>Q3/Q4</t>
-  </si>
-  <si>
-    <t>Wen et al. (2023)</t>
-  </si>
-  <si>
-    <t>An approach to internal threats detection based on sentiment and network analysis</t>
-  </si>
-  <si>
-    <t>Journal of Info. Security &amp; Apps</t>
-  </si>
-  <si>
-    <t>Kim et al. (2023)</t>
-  </si>
-  <si>
-    <t>Real-time insider threat detection system based on log analysis</t>
-  </si>
-  <si>
-    <t>Lin et al. (2024)</t>
-  </si>
-  <si>
-    <t>A Robust and Privacy-Preserving User-Centric Framework...</t>
-  </si>
-  <si>
-    <t>Gadekallu et al. (2024)</t>
-  </si>
-  <si>
-    <t>Deep learning based insider threat detection for industrial IoT</t>
-  </si>
-  <si>
-    <t>Lee et al. (2024)</t>
-  </si>
-  <si>
-    <t>Enhanced anomaly detection using expert systems...</t>
-  </si>
-  <si>
-    <t>Expert Systems with Apps.</t>
-  </si>
-  <si>
     <t>An approach to internal threats detection based on sentiment analysis and network analysis</t>
   </si>
   <si>
@@ -563,178 +424,6 @@
   </si>
   <si>
     <t>Others</t>
-  </si>
-  <si>
-    <t>Rank</t>
-  </si>
-  <si>
-    <t>Keyword / Theme</t>
-  </si>
-  <si>
-    <r>
-      <t>Frequency (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="14.5"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>f</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Coverage % (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="14.5"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>f</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14.5"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>/82</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>Relative %¹</t>
-  </si>
-  <si>
-    <t>Primary Representative Citations</t>
-  </si>
-  <si>
-    <t>Anomaly Detection</t>
-  </si>
-  <si>
-    <t>Al-Shehari (2024), Ahmad (2025), Alshehari (2023), Amiri-Zarandi (2023), Asha S (2023) [+ 37 more]</t>
-  </si>
-  <si>
-    <t>Nasir (2021), Lavanya (2024), He (2024), Kotb (2025), Yuan (2018) [+ 35 more]</t>
-  </si>
-  <si>
-    <t>Amuda (2022), Roy (2024), Greitzer (2011), Nasir (2021), Rauf (2021) [+ 19 more]</t>
-  </si>
-  <si>
-    <t>Graph Neural Networks</t>
-  </si>
-  <si>
-    <t>Xiao F (2025), Xiao J (2023), Li X (2023), Cai (2024), roy (2024) [+ 16 more]</t>
-  </si>
-  <si>
-    <t>Le (2021), Al-Mhiqani (2022), Ali (2025), Randive (2023), Senevirantha (2025) [+ 14 more]</t>
-  </si>
-  <si>
-    <t>Al-Shehari (2024), Asha S (2023), Jaiswal (2024), Pal (2023), Sarhan (2022) [+ 12 more]</t>
-  </si>
-  <si>
-    <t>Federated Learning</t>
-  </si>
-  <si>
-    <t>Ye (2025), Gupta (2024), Kamatchi (2025), Wang Zhi (2024), Ahmadi (2025) [+ 7 more]</t>
-  </si>
-  <si>
-    <t>NLP / Sentiment Analysis</t>
-  </si>
-  <si>
-    <t>Haq (2022), Ali (2025), Janjua (2021), Wen X (2023), Mladenovic (2024) [+ 4 more]</t>
-  </si>
-  <si>
-    <t>Explainable AI (XAI)</t>
-  </si>
-  <si>
-    <t>Gayathari (2025), Amiri-Zarandi (2023), Kotb (2025), Alhammadi (2021), Neupane (2022) [+ 3 more]</t>
-  </si>
-  <si>
-    <t>IoT Security</t>
-  </si>
-  <si>
-    <t>Tukur (2021), Anju (2024), Kamatchi (2025), Kong (2025), Al-Hawawreh (2022) [+ 2 more]</t>
-  </si>
-  <si>
-    <r>
-      <t>Total Sum of Mentions (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14.5"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>total</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>​</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>Final synthesis for PhD Treemap calibration.</t>
-  </si>
-  <si>
-    <t>Deep Learning</t>
-  </si>
-  <si>
-    <t>Behavioral Analysis</t>
-  </si>
-  <si>
-    <t>Data Imbalance Handling</t>
-  </si>
-  <si>
-    <t>Ensemble Learning</t>
   </si>
   <si>
     <t>Publication Year</t>
@@ -1200,10 +889,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1256,54 +942,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="14.5"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14.5"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="14.5"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1319,7 +957,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1342,64 +980,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
@@ -1452,30 +1037,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2030,399 +1593,6 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ar-OM"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:pieChart>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Publisher Source '!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Paper Count</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-F04F-45C0-8ECF-DC995F6930FA}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-F04F-45C0-8ECF-DC995F6930FA}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-F04F-45C0-8ECF-DC995F6930FA}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="3"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-F04F-45C0-8ECF-DC995F6930FA}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="4"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-F04F-45C0-8ECF-DC995F6930FA}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="5"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-F04F-45C0-8ECF-DC995F6930FA}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="ar-OM"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="1"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="35000"/>
-                      <a:lumOff val="65000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:round/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Publisher Source '!$A$2:$A$7</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>IEEE</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Elsevier</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>MDPI</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Nature</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Springer</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Other</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Publisher Source '!$B$2:$B$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>28</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000C-F04F-45C0-8ECF-DC995F6930FA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="ctr"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
-        </c:dLbls>
-        <c:firstSliceAng val="0"/>
-      </c:pieChart>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ar-OM"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="ar-OM"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
@@ -2709,546 +1879,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ar-OM"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Journal Namd and Paper Count'!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Number of Papers</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Journal Namd and Paper Count'!$A$2:$A$46</c:f>
-              <c:strCache>
-                <c:ptCount val="45"/>
-                <c:pt idx="0">
-                  <c:v>IEEE ACCESS</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>SCIENTIFIC REPORTS</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Computers &amp; Security</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>IEEE TRANSACTIONS ON INFORMATION FORENSICS AND SECURITY</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>IEEE Transactions on Dependable and Secure Computing</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>APPLIED SCIENCES-BASEL</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>INTERNATIONAL JOURNAL OF ADVANCED COMPUTER SCIENCE AND APPLICATIONS</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Computers and Electrical Engineering</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>EXPERT SYSTEMS WITH APPLICATIONS</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>IEEE Transactions on Network and Service Management</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Future Generation Computer Systems</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>IEEE INTERNET OF THINGS JOURNAL</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>IEEE TRANSACTIONS ON INDUSTRIAL INFORMATICS</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Future Internet</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Cybersecurity</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>INTERNATIONAL JOURNAL OF INFORMATION SECURITY</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>JOURNAL OF INFORMATION SECURITY AND APPLICATIONS</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>AD HOC NETWORKS</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Applied Soft Computing</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>ENGINEERING APPLICATIONS OF ARTIFICIAL INTELLIGENCE</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>IEEE Network</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>IEEE TRANSACTIONS ON NETWORK SCIENCE AND ENGINEERING</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>INTERNET OF THINGS</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>KNOWLEDGE-BASED SYSTEMS</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>Sustainable Energy Technologies and Assessments</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>BMC Medical Informatics and Decision Making</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>Entropy</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>JOURNAL OF NETWORK AND SYSTEMS MANAGEMENT</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>Mobile Networks and Applications</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>ANNALS OF TELECOMMUNICATIONS</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>COMPUTER SYSTEMS SCIENCE AND ENGINEERING</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>Forensic Science International: Digital Investigation</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>Journal of Supercomputing</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>WIRELESS NETWORKS</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>Intelligent Automation and Soft Computing</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>Cyber Security and Applications</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>International Journal of Applied Decision Sciences</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>International Journal of Communication Networks and Information Security</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>International Journal of Computer Network and Information Security</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>International Journal of Electrical and Electronic Engineering and Telecommunications</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>International Journal of Engineering Trends and Technology</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>International Journal of Innovative Technology and Interdisciplinary Sciences</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>Journal of Theoretical and Applied Information Technology</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>Journal of Wireless Mobile Networks, Ubiquitous Computing, and Dependable Applications</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>NIPES – Journal of Science and Technology Research</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Journal Namd and Paper Count'!$B$2:$B$46</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="45"/>
-                <c:pt idx="0">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A443-4E14-A242-AF200E09ACD6}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="182"/>
-        <c:axId val="805503391"/>
-        <c:axId val="805500991"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="805503391"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ar-OM"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="805500991"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="805500991"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ar-OM"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="805503391"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="ar-OM"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
@@ -3654,7 +2285,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
@@ -4055,81 +2686,6 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
-  <cx:chartData>
-    <cx:data id="0">
-      <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.0</cx:f>
-      </cx:strDim>
-      <cx:numDim type="size">
-        <cx:f>_xlchart.v1.2</cx:f>
-      </cx:numDim>
-    </cx:data>
-  </cx:chartData>
-  <cx:chart>
-    <cx:title pos="t" align="ctr" overlay="0"/>
-    <cx:plotArea>
-      <cx:plotAreaRegion>
-        <cx:series layoutId="treemap" uniqueId="{B6D8E7CC-D397-444D-844C-2BCD048DC860}">
-          <cx:tx>
-            <cx:txData>
-              <cx:f>_xlchart.v1.1</cx:f>
-              <cx:v>Relative %¹</cx:v>
-            </cx:txData>
-          </cx:tx>
-          <cx:dataLabels pos="inEnd">
-            <cx:txPr>
-              <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr algn="ctr" rtl="0">
-                  <a:defRPr sz="9600"/>
-                </a:pPr>
-                <a:endParaRPr lang="en-GB" sz="9600" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="window" lastClr="FFFFFF"/>
-                  </a:solidFill>
-                  <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-                </a:endParaRPr>
-              </a:p>
-            </cx:txPr>
-            <cx:visibility seriesName="0" categoryName="1" value="1"/>
-            <cx:separator>, </cx:separator>
-            <cx:dataLabel idx="0">
-              <cx:txPr>
-                <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr algn="ctr" rtl="0">
-                    <a:defRPr sz="1600"/>
-                  </a:pPr>
-                  <a:r>
-                    <a:rPr lang="en-GB" sz="1600" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                      <a:solidFill>
-                        <a:sysClr val="window" lastClr="FFFFFF"/>
-                      </a:solidFill>
-                      <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-                    </a:rPr>
-                    <a:t> Anomaly Detection , 21.11%</a:t>
-                  </a:r>
-                </a:p>
-              </cx:txPr>
-              <cx:visibility seriesName="0" categoryName="1" value="1"/>
-              <cx:separator>, </cx:separator>
-            </cx:dataLabel>
-          </cx:dataLabels>
-          <cx:dataId val="0"/>
-          <cx:layoutPr>
-            <cx:parentLabelLayout val="overlapping"/>
-          </cx:layoutPr>
-        </cx:series>
-      </cx:plotAreaRegion>
-    </cx:plotArea>
-  </cx:chart>
-</cx:chartSpace>
-</file>
-
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -4290,126 +2846,6 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
@@ -4930,525 +3366,6 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="204">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6015,8 +3932,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="225">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -6027,7 +3944,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -6050,14 +3967,14 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900" b="0" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -6073,7 +3990,507 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="38100" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="8"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="major">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="2000" b="0" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="340">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -6117,35 +4534,35 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="34925" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -6157,30 +4574,31 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -6214,1034 +4632,6 @@
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="225">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200" cap="all"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" b="0" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="38100" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="8"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="major">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="2000" b="0" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="410">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1">
-          <a:lumMod val="65000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
   </cs:dataTable>
   <cs:downBar>
     <cs:lnRef idx="0"/>
@@ -7310,7 +4700,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
@@ -7343,8 +4733,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -7399,22 +4789,22 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -7428,7 +4818,7 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
@@ -7438,7 +4828,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
     <cs:lnRef idx="0"/>
@@ -7448,9 +4838,12 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:srgbClr val="D9D9D9"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
@@ -7466,7 +4859,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400"/>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -7475,14 +4868,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDash"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -7496,7 +4888,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
   <cs:upBar>
     <cs:lnRef idx="0"/>
@@ -7529,508 +4921,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="340">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="34925" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -8048,16 +4938,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>52387</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>348494</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>103518</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>23812</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2513556</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>130413</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8082,44 +4972,6 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>353786</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>40822</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>331561</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>68489</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E4C87B5-F5A8-4DA6-A3EE-2C4E43ED9379}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8127,16 +4979,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>390525</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>168275</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>430212</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>500062</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8168,52 +5020,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>349250</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>58737</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>4761</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A282B53-4318-6117-BD57-C4A01EDDF222}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>131618</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>533399</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:colOff>266699</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>17461</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8232,7 +5048,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8245,99 +5061,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>449942</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>1141186</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>322449</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>72278</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>65</xdr:col>
-      <xdr:colOff>63500</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="2" name="Chart 1">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90EFD67D-6C65-8BB2-25AE-194DA85109D3}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="13448392" y="988786"/>
-              <a:ext cx="35110058" cy="25243064"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="ar-OM" sz="1100"/>
-                <a:t>This chart isn’t available in your version of Excel.
-Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>26987</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>111125</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1587</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>306761</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104028</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8681,358 +5414,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F992EDCC-6B15-4E47-85DB-07A5C1D643A7}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="18.25" customWidth="1"/>
-    <col min="3" max="3" width="43" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F204030D-709A-41CF-BCD4-DB7E80BE5442}">
   <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -9043,156 +5424,156 @@
   <sheetData>
     <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="B3" s="3">
         <v>1</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="23.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
@@ -9206,35 +5587,35 @@
         <v>8</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="B13" s="4">
         <v>4</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="B14" s="4">
         <v>3</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>136</v>
+        <v>92</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
@@ -9248,21 +5629,21 @@
         <v>18</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
@@ -9276,35 +5657,35 @@
         <v>12</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="B18" s="3">
         <v>2</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="B19" s="3">
         <v>2</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
@@ -9318,21 +5699,21 @@
         <v>4</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="B21" s="3">
         <v>2</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
@@ -9346,35 +5727,35 @@
         <v>16</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="B23" s="3">
         <v>1</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="B24" s="3">
         <v>1</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
@@ -9388,77 +5769,77 @@
         <v>10</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="B26" s="3">
         <v>1</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="B27" s="3">
         <v>1</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>153</v>
+        <v>109</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="B28" s="3">
         <v>1</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="B29" s="3">
         <v>1</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>159</v>
+        <v>115</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="B30" s="3">
         <v>1</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
@@ -9472,7 +5853,7 @@
         <v>6</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.5" x14ac:dyDescent="0.3">
@@ -9486,49 +5867,49 @@
         <v>2</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="B33" s="3">
         <v>2</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="B34" s="3">
         <v>2</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>149</v>
+        <v>105</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="B35" s="3">
         <v>2</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15.5" x14ac:dyDescent="0.3">
@@ -9542,161 +5923,161 @@
         <v>14</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="B37" s="3">
         <v>1</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="B38" s="3">
         <v>1</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="B39" s="3">
         <v>1</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>157</v>
+        <v>113</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="B40" s="3">
         <v>1</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="B41" s="3">
         <v>3</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>140</v>
+        <v>96</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="B42" s="3">
         <v>1</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="B43" s="3">
         <v>1</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="B44" s="3">
         <v>1</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="B45" s="3">
         <v>1</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="B46" s="3">
         <v>1</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="B47" s="3">
         <v>1</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>141</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -9714,7 +6095,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D71BD0A-D50C-442E-8923-35E9F05434AE}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -9725,79 +6106,79 @@
   <sheetData>
     <row r="1" spans="1:3" ht="42.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="B2" s="9">
         <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="B3" s="9">
         <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="B4" s="9">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="B5" s="9">
         <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="B6" s="9">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>129</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>130</v>
+        <v>86</v>
       </c>
       <c r="B7" s="9">
         <v>28</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>131</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -9806,7 +6187,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75E9CDCC-A5A8-4B70-9EEF-3D6E2D2BD80E}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -9818,18 +6199,18 @@
   <sheetData>
     <row r="1" spans="1:3" ht="42.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>164</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>165</v>
+        <v>121</v>
       </c>
       <c r="B2" s="2">
         <v>37</v>
@@ -9840,7 +6221,7 @@
     </row>
     <row r="3" spans="1:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>166</v>
+        <v>122</v>
       </c>
       <c r="B3" s="2">
         <v>26</v>
@@ -9851,7 +6232,7 @@
     </row>
     <row r="4" spans="1:3" ht="42.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>167</v>
+        <v>123</v>
       </c>
       <c r="B4" s="2">
         <v>8</v>
@@ -9862,7 +6243,7 @@
     </row>
     <row r="5" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>168</v>
+        <v>124</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -9873,7 +6254,7 @@
     </row>
     <row r="6" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>169</v>
+        <v>125</v>
       </c>
       <c r="B6" s="2">
         <v>10</v>
@@ -9884,7 +6265,7 @@
     </row>
     <row r="7" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>170</v>
+        <v>126</v>
       </c>
       <c r="B7" s="1">
         <v>82</v>
@@ -9899,7 +6280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E72D6E66-91BE-4AB5-B482-6161493422D8}">
   <dimension ref="A1:R47"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -9914,10 +6295,10 @@
   <sheetData>
     <row r="1" spans="1:18" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:18" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
@@ -9938,7 +6319,7 @@
     </row>
     <row r="4" spans="1:18" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="B4" s="2">
         <v>4</v>
@@ -9954,16 +6335,16 @@
     </row>
     <row r="6" spans="1:18" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="B6" s="2">
         <v>3</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:18" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
@@ -9974,7 +6355,7 @@
         <v>3</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="R7" s="2">
         <v>1</v>
@@ -9982,7 +6363,7 @@
     </row>
     <row r="8" spans="1:18" s="17" customFormat="1" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="B8" s="2">
         <v>3</v>
@@ -9996,13 +6377,13 @@
     </row>
     <row r="9" spans="1:18" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="B9" s="2">
         <v>3</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="R9" s="2">
         <v>2</v>
@@ -10016,7 +6397,7 @@
         <v>2</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="R10" s="2">
         <v>2</v>
@@ -10024,7 +6405,7 @@
     </row>
     <row r="11" spans="1:18" s="17" customFormat="1" ht="42.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="B11" s="2">
         <v>2</v>
@@ -10038,13 +6419,13 @@
     </row>
     <row r="12" spans="1:18" s="17" customFormat="1" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="R12" s="2">
         <v>2</v>
@@ -10058,7 +6439,7 @@
         <v>2</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="R13" s="2">
         <v>2</v>
@@ -10066,13 +6447,13 @@
     </row>
     <row r="14" spans="1:18" s="17" customFormat="1" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="R14" s="2">
         <v>2</v>
@@ -10080,13 +6461,13 @@
     </row>
     <row r="15" spans="1:18" s="17" customFormat="1" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="R15" s="2">
         <v>2</v>
@@ -10094,7 +6475,7 @@
     </row>
     <row r="16" spans="1:18" s="17" customFormat="1" ht="42.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="B16" s="2">
         <v>2</v>
@@ -10108,13 +6489,13 @@
     </row>
     <row r="17" spans="1:18" s="17" customFormat="1" ht="42.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="B17" s="2">
         <v>2</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="R17" s="2">
         <v>3</v>
@@ -10142,7 +6523,7 @@
         <v>1</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="R19" s="2">
         <v>3</v>
@@ -10150,13 +6531,13 @@
     </row>
     <row r="20" spans="1:18" s="17" customFormat="1" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="B20" s="2">
         <v>1</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="R20" s="2">
         <v>3</v>
@@ -10170,7 +6551,7 @@
         <v>1</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="R21" s="2">
         <v>4</v>
@@ -10178,7 +6559,7 @@
     </row>
     <row r="22" spans="1:18" s="17" customFormat="1" ht="56.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="B22" s="2">
         <v>1</v>
@@ -10192,7 +6573,7 @@
     </row>
     <row r="23" spans="1:18" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="B23" s="2">
         <v>1</v>
@@ -10206,7 +6587,7 @@
     </row>
     <row r="24" spans="1:18" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="B24" s="2">
         <v>1</v>
@@ -10220,7 +6601,7 @@
     </row>
     <row r="25" spans="1:18" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="B25" s="2">
         <v>1</v>
@@ -10228,7 +6609,7 @@
     </row>
     <row r="26" spans="1:18" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="B26" s="2">
         <v>1</v>
@@ -10236,7 +6617,7 @@
     </row>
     <row r="27" spans="1:18" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="B27" s="2">
         <v>1</v>
@@ -10244,7 +6625,7 @@
     </row>
     <row r="28" spans="1:18" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="B28" s="2">
         <v>1</v>
@@ -10252,7 +6633,7 @@
     </row>
     <row r="29" spans="1:18" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="B29" s="2">
         <v>1</v>
@@ -10260,7 +6641,7 @@
     </row>
     <row r="30" spans="1:18" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="B30" s="2">
         <v>1</v>
@@ -10268,7 +6649,7 @@
     </row>
     <row r="31" spans="1:18" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="B31" s="2">
         <v>1</v>
@@ -10276,7 +6657,7 @@
     </row>
     <row r="32" spans="1:18" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="B32" s="2">
         <v>1</v>
@@ -10284,7 +6665,7 @@
     </row>
     <row r="33" spans="1:2" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="B33" s="2">
         <v>1</v>
@@ -10292,7 +6673,7 @@
     </row>
     <row r="34" spans="1:2" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="B34" s="2">
         <v>1</v>
@@ -10300,7 +6681,7 @@
     </row>
     <row r="35" spans="1:2" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="B35" s="2">
         <v>1</v>
@@ -10308,7 +6689,7 @@
     </row>
     <row r="36" spans="1:2" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="B36" s="2">
         <v>1</v>
@@ -10316,7 +6697,7 @@
     </row>
     <row r="37" spans="1:2" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="B37" s="2">
         <v>1</v>
@@ -10324,7 +6705,7 @@
     </row>
     <row r="38" spans="1:2" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="B38" s="2">
         <v>1</v>
@@ -10332,7 +6713,7 @@
     </row>
     <row r="39" spans="1:2" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="B39" s="2">
         <v>1</v>
@@ -10340,7 +6721,7 @@
     </row>
     <row r="40" spans="1:2" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="B40" s="2">
         <v>1</v>
@@ -10348,7 +6729,7 @@
     </row>
     <row r="41" spans="1:2" s="17" customFormat="1" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="B41" s="2">
         <v>1</v>
@@ -10356,7 +6737,7 @@
     </row>
     <row r="42" spans="1:2" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="B42" s="2">
         <v>1</v>
@@ -10364,7 +6745,7 @@
     </row>
     <row r="43" spans="1:2" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="B43" s="2">
         <v>1</v>
@@ -10372,7 +6753,7 @@
     </row>
     <row r="44" spans="1:2" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="B44" s="2">
         <v>1</v>
@@ -10380,7 +6761,7 @@
     </row>
     <row r="45" spans="1:2" s="17" customFormat="1" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="B45" s="2">
         <v>1</v>
@@ -10388,7 +6769,7 @@
     </row>
     <row r="46" spans="1:2" s="17" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="B46" s="2">
         <v>1</v>
@@ -10396,7 +6777,7 @@
     </row>
     <row r="47" spans="1:2" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>170</v>
+        <v>126</v>
       </c>
       <c r="B47" s="1">
         <v>82</v>
@@ -10411,265 +6792,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E42D1F3-530E-4360-956F-622B34BF85FB}">
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="20.25" customWidth="1"/>
-    <col min="3" max="3" width="16.08203125" customWidth="1"/>
-    <col min="4" max="4" width="21.5" customWidth="1"/>
-    <col min="5" max="5" width="29.83203125" customWidth="1"/>
-    <col min="6" max="6" width="31.08203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="30.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="B1" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="C1" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="F1" s="19" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="47" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="20">
-        <v>1</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="C2" s="21">
-        <v>42</v>
-      </c>
-      <c r="D2" s="22">
-        <v>0.51200000000000001</v>
-      </c>
-      <c r="E2" s="22">
-        <v>0.21110000000000001</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="47" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="20">
-        <v>2</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="C3" s="21">
-        <v>40</v>
-      </c>
-      <c r="D3" s="22">
-        <v>0.48799999999999999</v>
-      </c>
-      <c r="E3" s="22">
-        <v>0.20100000000000001</v>
-      </c>
-      <c r="F3" s="23" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="47" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="20">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="C4" s="21">
-        <v>24</v>
-      </c>
-      <c r="D4" s="22">
-        <v>0.29299999999999998</v>
-      </c>
-      <c r="E4" s="22">
-        <v>0.1206</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="186.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="20">
-        <v>4</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="C5" s="21">
-        <v>21</v>
-      </c>
-      <c r="D5" s="22">
-        <v>0.25600000000000001</v>
-      </c>
-      <c r="E5" s="22">
-        <v>0.1055</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="47" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="20">
-        <v>5</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="C6" s="21">
-        <v>19</v>
-      </c>
-      <c r="D6" s="22">
-        <v>0.23200000000000001</v>
-      </c>
-      <c r="E6" s="22">
-        <v>9.5500000000000002E-2</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="47" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="20">
-        <v>6</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="C7" s="21">
-        <v>17</v>
-      </c>
-      <c r="D7" s="22">
-        <v>0.20699999999999999</v>
-      </c>
-      <c r="E7" s="22">
-        <v>8.5400000000000004E-2</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="202" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="20">
-        <v>7</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="C8" s="21">
-        <v>12</v>
-      </c>
-      <c r="D8" s="22">
-        <v>0.14599999999999999</v>
-      </c>
-      <c r="E8" s="22">
-        <v>6.0299999999999999E-2</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="202" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="20">
-        <v>8</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="C9" s="21">
-        <v>9</v>
-      </c>
-      <c r="D9" s="22">
-        <v>0.11</v>
-      </c>
-      <c r="E9" s="22">
-        <v>4.5199999999999997E-2</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="217.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="20">
-        <v>9</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="C10" s="21">
-        <v>8</v>
-      </c>
-      <c r="D10" s="22">
-        <v>9.8000000000000004E-2</v>
-      </c>
-      <c r="E10" s="22">
-        <v>4.02E-2</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="202" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="20">
-        <v>10</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="C11" s="21">
-        <v>7</v>
-      </c>
-      <c r="D11" s="22">
-        <v>8.5000000000000006E-2</v>
-      </c>
-      <c r="E11" s="22">
-        <v>3.5200000000000002E-2</v>
-      </c>
-      <c r="F11" s="23" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="34" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="C12" s="21">
-        <v>199</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="E12" s="22">
-        <v>1</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>195</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F072533B-AB61-4A3E-AFC5-79FEFE808565}">
   <dimension ref="A1:R83"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -10681,13 +6804,13 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>200</v>
+        <v>128</v>
       </c>
       <c r="B1" t="s">
-        <v>201</v>
+        <v>129</v>
       </c>
       <c r="C1" t="s">
-        <v>202</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -10695,10 +6818,10 @@
         <v>2021</v>
       </c>
       <c r="B2" t="s">
-        <v>203</v>
+        <v>131</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -10706,10 +6829,10 @@
         <v>2021</v>
       </c>
       <c r="B3" t="s">
-        <v>235</v>
+        <v>163</v>
       </c>
       <c r="C3" t="s">
-        <v>236</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -10717,10 +6840,10 @@
         <v>2021</v>
       </c>
       <c r="B4" t="s">
-        <v>239</v>
+        <v>167</v>
       </c>
       <c r="C4" t="s">
-        <v>240</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -10728,10 +6851,10 @@
         <v>2021</v>
       </c>
       <c r="B5" t="s">
-        <v>241</v>
+        <v>169</v>
       </c>
       <c r="C5" t="s">
-        <v>242</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -10739,10 +6862,10 @@
         <v>2021</v>
       </c>
       <c r="B6" t="s">
-        <v>243</v>
+        <v>171</v>
       </c>
       <c r="C6" t="s">
-        <v>244</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -10750,10 +6873,10 @@
         <v>2021</v>
       </c>
       <c r="B7" t="s">
-        <v>249</v>
+        <v>177</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -10761,10 +6884,10 @@
         <v>2021</v>
       </c>
       <c r="B8" t="s">
-        <v>274</v>
+        <v>202</v>
       </c>
       <c r="C8" t="s">
-        <v>275</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -10772,10 +6895,10 @@
         <v>2021</v>
       </c>
       <c r="B9" t="s">
-        <v>293</v>
+        <v>221</v>
       </c>
       <c r="C9" t="s">
-        <v>294</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -10783,10 +6906,10 @@
         <v>2021</v>
       </c>
       <c r="B10" t="s">
-        <v>299</v>
+        <v>227</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -10794,10 +6917,10 @@
         <v>2021</v>
       </c>
       <c r="B11" t="s">
-        <v>330</v>
+        <v>258</v>
       </c>
       <c r="C11" t="s">
-        <v>331</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -10805,10 +6928,10 @@
         <v>2022</v>
       </c>
       <c r="B12" t="s">
-        <v>213</v>
+        <v>141</v>
       </c>
       <c r="C12" t="s">
-        <v>214</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -10816,10 +6939,10 @@
         <v>2022</v>
       </c>
       <c r="B13" t="s">
-        <v>219</v>
+        <v>147</v>
       </c>
       <c r="C13" t="s">
-        <v>220</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -10827,19 +6950,19 @@
         <v>2022</v>
       </c>
       <c r="B14" t="s">
-        <v>262</v>
+        <v>190</v>
       </c>
       <c r="C14" t="s">
-        <v>263</v>
+        <v>191</v>
       </c>
       <c r="P14" t="s">
-        <v>350</v>
+        <v>278</v>
       </c>
       <c r="Q14" t="s">
-        <v>351</v>
+        <v>279</v>
       </c>
       <c r="R14" t="s">
-        <v>352</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -10847,10 +6970,10 @@
         <v>2022</v>
       </c>
       <c r="B15" t="s">
-        <v>272</v>
+        <v>200</v>
       </c>
       <c r="C15" t="s">
-        <v>273</v>
+        <v>201</v>
       </c>
       <c r="P15">
         <v>2021</v>
@@ -10868,10 +6991,10 @@
         <v>2022</v>
       </c>
       <c r="B16" t="s">
-        <v>297</v>
+        <v>225</v>
       </c>
       <c r="C16" t="s">
-        <v>298</v>
+        <v>226</v>
       </c>
       <c r="P16">
         <v>2022</v>
@@ -10889,10 +7012,10 @@
         <v>2022</v>
       </c>
       <c r="B17" t="s">
-        <v>300</v>
+        <v>228</v>
       </c>
       <c r="C17" t="s">
-        <v>301</v>
+        <v>229</v>
       </c>
       <c r="P17">
         <v>2023</v>
@@ -10910,10 +7033,10 @@
         <v>2022</v>
       </c>
       <c r="B18" t="s">
-        <v>306</v>
+        <v>234</v>
       </c>
       <c r="C18" t="s">
-        <v>307</v>
+        <v>235</v>
       </c>
       <c r="P18">
         <v>2024</v>
@@ -10931,10 +7054,10 @@
         <v>2022</v>
       </c>
       <c r="B19" t="s">
-        <v>316</v>
+        <v>244</v>
       </c>
       <c r="C19" t="s">
-        <v>317</v>
+        <v>245</v>
       </c>
       <c r="P19">
         <v>2025</v>
@@ -10952,10 +7075,10 @@
         <v>2022</v>
       </c>
       <c r="B20" t="s">
-        <v>347</v>
+        <v>275</v>
       </c>
       <c r="C20" t="s">
-        <v>348</v>
+        <v>276</v>
       </c>
       <c r="Q20">
         <f>SUM(Q15:Q19)</f>
@@ -10967,10 +7090,10 @@
         <v>2023</v>
       </c>
       <c r="B21" t="s">
-        <v>207</v>
+        <v>135</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -10978,10 +7101,10 @@
         <v>2023</v>
       </c>
       <c r="B22" t="s">
-        <v>208</v>
+        <v>136</v>
       </c>
       <c r="C22" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -10989,10 +7112,10 @@
         <v>2023</v>
       </c>
       <c r="B23" t="s">
-        <v>215</v>
+        <v>143</v>
       </c>
       <c r="C23" t="s">
-        <v>216</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -11000,10 +7123,10 @@
         <v>2023</v>
       </c>
       <c r="B24" t="s">
-        <v>238</v>
+        <v>166</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
@@ -11011,10 +7134,10 @@
         <v>2023</v>
       </c>
       <c r="B25" t="s">
-        <v>250</v>
+        <v>178</v>
       </c>
       <c r="C25" t="s">
-        <v>251</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
@@ -11022,10 +7145,10 @@
         <v>2023</v>
       </c>
       <c r="B26" t="s">
-        <v>254</v>
+        <v>182</v>
       </c>
       <c r="C26" t="s">
-        <v>255</v>
+        <v>183</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -11033,10 +7156,10 @@
         <v>2023</v>
       </c>
       <c r="B27" t="s">
-        <v>260</v>
+        <v>188</v>
       </c>
       <c r="C27" t="s">
-        <v>261</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
@@ -11044,10 +7167,10 @@
         <v>2023</v>
       </c>
       <c r="B28" t="s">
-        <v>268</v>
+        <v>196</v>
       </c>
       <c r="C28" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
@@ -11055,10 +7178,10 @@
         <v>2023</v>
       </c>
       <c r="B29" t="s">
-        <v>278</v>
+        <v>206</v>
       </c>
       <c r="C29" t="s">
-        <v>279</v>
+        <v>207</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
@@ -11066,10 +7189,10 @@
         <v>2023</v>
       </c>
       <c r="B30" t="s">
-        <v>285</v>
+        <v>213</v>
       </c>
       <c r="C30" t="s">
-        <v>286</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
@@ -11077,10 +7200,10 @@
         <v>2023</v>
       </c>
       <c r="B31" t="s">
-        <v>291</v>
+        <v>219</v>
       </c>
       <c r="C31" t="s">
-        <v>292</v>
+        <v>220</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
@@ -11088,10 +7211,10 @@
         <v>2023</v>
       </c>
       <c r="B32" t="s">
-        <v>314</v>
+        <v>242</v>
       </c>
       <c r="C32" t="s">
-        <v>315</v>
+        <v>243</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -11099,10 +7222,10 @@
         <v>2023</v>
       </c>
       <c r="B33" t="s">
-        <v>320</v>
+        <v>248</v>
       </c>
       <c r="C33" t="s">
-        <v>321</v>
+        <v>249</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -11110,10 +7233,10 @@
         <v>2023</v>
       </c>
       <c r="B34" t="s">
-        <v>322</v>
+        <v>250</v>
       </c>
       <c r="C34" t="s">
-        <v>323</v>
+        <v>251</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -11121,10 +7244,10 @@
         <v>2023</v>
       </c>
       <c r="B35" t="s">
-        <v>324</v>
+        <v>252</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -11132,10 +7255,10 @@
         <v>2023</v>
       </c>
       <c r="B36" t="s">
-        <v>336</v>
+        <v>264</v>
       </c>
       <c r="C36" t="s">
-        <v>337</v>
+        <v>265</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -11143,10 +7266,10 @@
         <v>2024</v>
       </c>
       <c r="B37" t="s">
-        <v>204</v>
+        <v>132</v>
       </c>
       <c r="C37" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -11154,10 +7277,10 @@
         <v>2024</v>
       </c>
       <c r="B38" t="s">
-        <v>209</v>
+        <v>137</v>
       </c>
       <c r="C38" t="s">
-        <v>210</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -11165,10 +7288,10 @@
         <v>2024</v>
       </c>
       <c r="B39" t="s">
-        <v>211</v>
+        <v>139</v>
       </c>
       <c r="C39" t="s">
-        <v>212</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -11176,10 +7299,10 @@
         <v>2024</v>
       </c>
       <c r="B40" t="s">
-        <v>217</v>
+        <v>145</v>
       </c>
       <c r="C40" t="s">
-        <v>218</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -11187,10 +7310,10 @@
         <v>2024</v>
       </c>
       <c r="B41" t="s">
-        <v>221</v>
+        <v>149</v>
       </c>
       <c r="C41" t="s">
-        <v>222</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -11198,10 +7321,10 @@
         <v>2024</v>
       </c>
       <c r="B42" t="s">
-        <v>231</v>
+        <v>159</v>
       </c>
       <c r="C42" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -11209,10 +7332,10 @@
         <v>2024</v>
       </c>
       <c r="B43" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -11220,10 +7343,10 @@
         <v>2024</v>
       </c>
       <c r="B44" t="s">
-        <v>252</v>
+        <v>180</v>
       </c>
       <c r="C44" t="s">
-        <v>253</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -11231,10 +7354,10 @@
         <v>2024</v>
       </c>
       <c r="B45" t="s">
-        <v>256</v>
+        <v>184</v>
       </c>
       <c r="C45" t="s">
-        <v>257</v>
+        <v>185</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -11242,10 +7365,10 @@
         <v>2024</v>
       </c>
       <c r="B46" t="s">
-        <v>258</v>
+        <v>186</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>187</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -11253,10 +7376,10 @@
         <v>2024</v>
       </c>
       <c r="B47" t="s">
-        <v>266</v>
+        <v>194</v>
       </c>
       <c r="C47" t="s">
-        <v>267</v>
+        <v>195</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -11264,10 +7387,10 @@
         <v>2024</v>
       </c>
       <c r="B48" t="s">
-        <v>276</v>
+        <v>204</v>
       </c>
       <c r="C48" t="s">
-        <v>277</v>
+        <v>205</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -11275,10 +7398,10 @@
         <v>2024</v>
       </c>
       <c r="B49" t="s">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="C49" t="s">
-        <v>281</v>
+        <v>209</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -11286,10 +7409,10 @@
         <v>2024</v>
       </c>
       <c r="B50" t="s">
-        <v>284</v>
+        <v>212</v>
       </c>
       <c r="C50" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -11297,10 +7420,10 @@
         <v>2024</v>
       </c>
       <c r="B51" t="s">
-        <v>287</v>
+        <v>215</v>
       </c>
       <c r="C51" t="s">
-        <v>288</v>
+        <v>216</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -11308,10 +7431,10 @@
         <v>2024</v>
       </c>
       <c r="B52" t="s">
-        <v>289</v>
+        <v>217</v>
       </c>
       <c r="C52" t="s">
-        <v>290</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -11319,10 +7442,10 @@
         <v>2024</v>
       </c>
       <c r="B53" t="s">
-        <v>310</v>
+        <v>238</v>
       </c>
       <c r="C53" t="s">
-        <v>311</v>
+        <v>239</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -11330,10 +7453,10 @@
         <v>2024</v>
       </c>
       <c r="B54" t="s">
-        <v>312</v>
+        <v>240</v>
       </c>
       <c r="C54" t="s">
-        <v>329</v>
+        <v>257</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -11341,10 +7464,10 @@
         <v>2024</v>
       </c>
       <c r="B55" t="s">
-        <v>334</v>
+        <v>262</v>
       </c>
       <c r="C55" t="s">
-        <v>335</v>
+        <v>263</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -11352,10 +7475,10 @@
         <v>2024</v>
       </c>
       <c r="B56" t="s">
-        <v>339</v>
+        <v>267</v>
       </c>
       <c r="C56" t="s">
-        <v>340</v>
+        <v>268</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -11363,10 +7486,10 @@
         <v>2024</v>
       </c>
       <c r="B57" t="s">
-        <v>341</v>
+        <v>269</v>
       </c>
       <c r="C57" t="s">
-        <v>342</v>
+        <v>270</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -11374,10 +7497,10 @@
         <v>2024</v>
       </c>
       <c r="B58" t="s">
-        <v>349</v>
+        <v>277</v>
       </c>
       <c r="C58" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -11385,10 +7508,10 @@
         <v>2025</v>
       </c>
       <c r="B59" t="s">
-        <v>205</v>
+        <v>133</v>
       </c>
       <c r="C59" t="s">
-        <v>206</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -11396,10 +7519,10 @@
         <v>2025</v>
       </c>
       <c r="B60" t="s">
-        <v>225</v>
+        <v>153</v>
       </c>
       <c r="C60" t="s">
-        <v>226</v>
+        <v>154</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -11407,10 +7530,10 @@
         <v>2025</v>
       </c>
       <c r="B61" t="s">
-        <v>227</v>
+        <v>155</v>
       </c>
       <c r="C61" t="s">
-        <v>228</v>
+        <v>156</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -11418,10 +7541,10 @@
         <v>2025</v>
       </c>
       <c r="B62" t="s">
-        <v>229</v>
+        <v>157</v>
       </c>
       <c r="C62" t="s">
-        <v>230</v>
+        <v>158</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -11429,10 +7552,10 @@
         <v>2025</v>
       </c>
       <c r="B63" t="s">
-        <v>232</v>
+        <v>160</v>
       </c>
       <c r="C63" t="s">
-        <v>233</v>
+        <v>161</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -11440,10 +7563,10 @@
         <v>2025</v>
       </c>
       <c r="B64" t="s">
-        <v>234</v>
+        <v>162</v>
       </c>
       <c r="C64" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -11451,10 +7574,10 @@
         <v>2025</v>
       </c>
       <c r="B65" t="s">
-        <v>245</v>
+        <v>173</v>
       </c>
       <c r="C65" t="s">
-        <v>246</v>
+        <v>174</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -11462,10 +7585,10 @@
         <v>2025</v>
       </c>
       <c r="B66" t="s">
-        <v>247</v>
+        <v>175</v>
       </c>
       <c r="C66" t="s">
-        <v>248</v>
+        <v>176</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
@@ -11473,10 +7596,10 @@
         <v>2025</v>
       </c>
       <c r="B67" t="s">
-        <v>264</v>
+        <v>192</v>
       </c>
       <c r="C67" t="s">
-        <v>265</v>
+        <v>193</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -11484,10 +7607,10 @@
         <v>2025</v>
       </c>
       <c r="B68" t="s">
-        <v>269</v>
+        <v>197</v>
       </c>
       <c r="C68" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -11495,10 +7618,10 @@
         <v>2025</v>
       </c>
       <c r="B69" t="s">
-        <v>270</v>
+        <v>198</v>
       </c>
       <c r="C69" t="s">
-        <v>271</v>
+        <v>199</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -11506,10 +7629,10 @@
         <v>2025</v>
       </c>
       <c r="B70" t="s">
-        <v>282</v>
+        <v>210</v>
       </c>
       <c r="C70" t="s">
-        <v>283</v>
+        <v>211</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -11517,10 +7640,10 @@
         <v>2025</v>
       </c>
       <c r="B71" t="s">
-        <v>295</v>
+        <v>223</v>
       </c>
       <c r="C71" t="s">
-        <v>296</v>
+        <v>224</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -11528,10 +7651,10 @@
         <v>2025</v>
       </c>
       <c r="B72" t="s">
-        <v>302</v>
+        <v>230</v>
       </c>
       <c r="C72" t="s">
-        <v>303</v>
+        <v>231</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -11539,10 +7662,10 @@
         <v>2025</v>
       </c>
       <c r="B73" t="s">
-        <v>304</v>
+        <v>232</v>
       </c>
       <c r="C73" t="s">
-        <v>305</v>
+        <v>233</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
@@ -11550,10 +7673,10 @@
         <v>2025</v>
       </c>
       <c r="B74" t="s">
-        <v>308</v>
+        <v>236</v>
       </c>
       <c r="C74" t="s">
-        <v>309</v>
+        <v>237</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -11561,10 +7684,10 @@
         <v>2025</v>
       </c>
       <c r="B75" t="s">
-        <v>312</v>
+        <v>240</v>
       </c>
       <c r="C75" t="s">
-        <v>313</v>
+        <v>241</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -11572,10 +7695,10 @@
         <v>2025</v>
       </c>
       <c r="B76" t="s">
-        <v>318</v>
+        <v>246</v>
       </c>
       <c r="C76" t="s">
-        <v>319</v>
+        <v>247</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -11583,10 +7706,10 @@
         <v>2025</v>
       </c>
       <c r="B77" t="s">
-        <v>325</v>
+        <v>253</v>
       </c>
       <c r="C77" t="s">
-        <v>326</v>
+        <v>254</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -11594,10 +7717,10 @@
         <v>2025</v>
       </c>
       <c r="B78" t="s">
-        <v>327</v>
+        <v>255</v>
       </c>
       <c r="C78" t="s">
-        <v>328</v>
+        <v>256</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -11605,10 +7728,10 @@
         <v>2025</v>
       </c>
       <c r="B79" t="s">
-        <v>332</v>
+        <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>333</v>
+        <v>261</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
@@ -11616,10 +7739,10 @@
         <v>2025</v>
       </c>
       <c r="B80" t="s">
-        <v>338</v>
+        <v>266</v>
       </c>
       <c r="C80" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
@@ -11627,10 +7750,10 @@
         <v>2025</v>
       </c>
       <c r="B81" t="s">
-        <v>343</v>
+        <v>271</v>
       </c>
       <c r="C81" t="s">
-        <v>344</v>
+        <v>272</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -11638,10 +7761,10 @@
         <v>2025</v>
       </c>
       <c r="B82" t="s">
-        <v>345</v>
+        <v>273</v>
       </c>
       <c r="C82" t="s">
-        <v>346</v>
+        <v>274</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
@@ -11649,10 +7772,10 @@
         <v>2025</v>
       </c>
       <c r="B83" t="s">
-        <v>223</v>
+        <v>151</v>
       </c>
       <c r="C83" t="s">
-        <v>224</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
